--- a/LangMod/EN/SourcePod.xlsx
+++ b/LangMod/EN/SourcePod.xlsx
@@ -695,7 +695,7 @@
   <dimension ref="A1:XFD5"/>
   <sheetFormatPr defaultColWidth="7.5078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="6.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="29.12"/>
@@ -711,7 +711,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="7.23"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="3" width="5.19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="6.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="2.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="10.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="8.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="6.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="42.29"/>
@@ -1127,7 +1127,7 @@
     <row r="3" s="10" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1"/>
       <c r="B3" s="3" t="n">
-        <f aca="false">MAX(B4:B9965)</f>
+        <f aca="false">MAX(B4:B9951)</f>
         <v>42000</v>
       </c>
       <c r="C3" s="5"/>

--- a/LangMod/EN/SourcePod.xlsx
+++ b/LangMod/EN/SourcePod.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -225,10 +225,10 @@
     <t xml:space="preserve">Friend</t>
   </si>
   <si>
-    <t xml:space="preserve">neutral,addStock,addZone_Kapul,addZone_TinkerCamp,addZone_Olvina,addZone_Aquli,addZone_Yowyn,addZone_Specwing,addZone_Mifu,addZone_Nefu,addZone_Palmia,addZone_Lothria,addZone_Mysilia,addZone_Derphy,addZone_Lumiest,addZone_Noyel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merchant</t>
+    <t xml:space="preserve">neutral,addZone_Kapul,addZone_TinkerCamp,addZone_Olvina,addZone_Aquli,addZone_Yowyn,addZone_Specwing,addZone_Mifu,addZone_Nefu,addZone_Palmia,addZone_Lothria,addZone_Mysilia,addZone_Derphy,addZone_Lumiest,addZone_Noyel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OmegaMerchantPod042</t>
   </si>
   <si>
     <t xml:space="preserve">metal</t>
@@ -262,6 +262,9 @@
   </si>
   <si>
     <t xml:space="preserve">Armor Merchant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OmegaMerchantPod153</t>
   </si>
   <si>
     <t xml:space="preserve">f</t>
@@ -715,7 +718,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="8.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="6.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="42.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="11.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="23.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="9.18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="8.06"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="6.53"/>
@@ -1330,7 +1333,7 @@
         <v>66</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="W5" s="1" t="s">
         <v>68</v>
@@ -1345,7 +1348,7 @@
         <v>71</v>
       </c>
       <c r="AN5" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR5" s="1" t="s">
         <v>73</v>
@@ -1397,34 +1400,34 @@
         <v>33</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1480,34 +1483,34 @@
         <v>73</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="1048302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
